--- a/evidence/excel-fidelity-inline-edit-v1/customer-quote-SYNTHETIC-edited.xlsx
+++ b/evidence/excel-fidelity-inline-edit-v1/customer-quote-SYNTHETIC-edited.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13.2" customWidth="1" min="5" max="5"/>
     <col width="49.50000000000001" customWidth="1" min="6" max="6"/>
-    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="40.7" customWidth="1" min="7" max="7"/>
     <col width="14.3" customWidth="1" min="8" max="8"/>
     <col width="35.2" customWidth="1" min="9" max="9"/>
   </cols>
@@ -564,12 +564,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>Kính gửi Quý công ty</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Công ty Lục Giác</t>
+          <t>Công ty Lục Giác — Chi nhánh Hà Nội</t>
         </is>
       </c>
     </row>
@@ -662,394 +662,392 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Phương án A: Khách tự đứng tên nhập khẩu</t>
+          <t>Dịch vụ trọn gói: vận chuyển biển + thủ tục nhập khẩu + giao tận kho.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Phương án A: Khách tự đứng tên nhập khẩu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Phạm vi dịch vụ đã xác nhận: Phạm vi đã thống nhất: vận chuyển và thủ tục nhập khẩu.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Cảng / điểm: Chưa xác nhận → Chưa xác nhận · Sea / FCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="18"/>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Cảng đi / cảng đến: Chưa xác nhận → Chưa xác nhận · Sea / FCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Nơi nhận hàng tại xưởng: Xưởng Nansha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Giao tại: Thanh Trì, Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>DANH MỤC HÀNG HÓA — giá theo bảng khách gửi</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Hàng hóa / Model / Vật liệu</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Dài mm</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Rộng mm</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Cao mm</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Đơn giá</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>Tiền tệ</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Thành tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Bàn họp nhập khẩu cao cấp · MS-C0242S · MDF + veneer</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>760</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>13055</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>208880</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Bàn họp văn phòng</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>760</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>18850</v>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>18850</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ghi chú hàng: Chưa xác nhận model/vật liệu</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Bàn họp văn phòng</t>
+          <t>Bàn họp nhập khẩu cao cấp · MS-C0242S · MDF + veneer</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>12000</v>
+        <v>5200</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>760</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>13055</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>208880</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Bàn họp văn phòng</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>760</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>18850</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>18850</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ghi chú hàng: Chưa xác nhận model/vật liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Bàn họp văn phòng</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>760</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>30150</v>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I27" s="7" t="n">
         <v>90450</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Ghi chú hàng: Chưa xác nhận model/vật liệu</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
+    <row r="29">
+      <c r="A29" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Bàn họp văn phòng</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C29" s="7" t="n">
         <v>16000</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D29" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>760</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F29" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G29" s="7" t="n">
         <v>40200</v>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I29" s="7" t="n">
         <v>241200</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Ghi chú hàng: Chưa xác nhận model/vật liệu</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
+    <row r="31">
+      <c r="A31" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Bàn họp văn phòng</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C31" s="7" t="n">
         <v>19000</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D31" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E31" s="7" t="n">
         <v>760</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G31" s="7" t="n">
         <v>47800</v>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I31" s="7" t="n">
         <v>47800</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Ghi chú hàng: Chưa xác nhận model/vật liệu</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Tổng tiền hàng CNY</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I33" t="n">
         <v>607180</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>PHÍ DỊCH VỤ — chỉ giá bán đã xác nhận</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Nội dung dịch vụ</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Đơn giá</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>Số lượng</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Thành tiền</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>thành tiền</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Đơn vị tiền</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Phát sinh (nếu có)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="n">
+    <row r="37">
+      <c r="A37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Vận chuyển Nansha → Hải Phòng</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C37" s="9" t="n">
         <v>35000000</v>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D37" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E37" s="9" t="n">
         <v>35000000</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G37" s="9" t="n">
         <v>37800000</v>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Đã gồm phí nâng hạ tại cảng đi</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG THEO TỪNG LOẠI TIỀN (không quy đổi gộp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Tổng VND</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>37800000</v>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>VND</t>
         </is>
       </c>
     </row>
@@ -1057,84 +1055,131 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>THUẾ NHẬP KHẨU DỰ KIẾN (không phải kết luận pháp lý)</t>
+          <t>TỔNG CỘNG THEO TỪNG LOẠI TIỀN (không quy đổi gộp)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Chưa xác định — trị giá hải quan / thuế suất chưa được xác nhận.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Tạm tính hàng + dịch vụ trước mọi thuế (VND)</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>2403002000</v>
-      </c>
-    </row>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Tổng VND</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>37800000</v>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>TỔNG DỰ TOÁN gồm thuế đã xác định (VND)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Chưa xác định</t>
+          <t>THUẾ NHẬP KHẨU DỰ KIẾN (không phải kết luận pháp lý)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
+          <t>Cơ sở hải quan riêng đã xác nhận: Chưa xác định — trị giá hải quan / thuế suất chưa được xác nhận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thuế NK dự kiến</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chưa xác định</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VAT NK dự kiến</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chưa xác định</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Tạm tính hàng + dịch vụ trước mọi thuế (VND)</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>2403002000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Tổng dự toán gồm thuế đã xác định (VND)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chưa xác định</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Đây là dự toán; không phải hóa đơn, khoản công nợ hay chứng từ xác nhận thuế.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Ghi chú:</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>- Thanh toán 70% trước khi giao hàng, 30% sau khi nhận hàng.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>- Sản xuất dự kiến 30 ngày.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>- Nhập khẩu dự kiến 14–20 ngày.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>- Có bản vẽ thiết kế sau một tuần kể từ khi đặt cọc.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>- Giao hàng tại kho khách
 Kiểm tra và ký biên bản bàn giao
@@ -1142,39 +1187,48 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>- Các khoản ghi “Phát sinh (nếu có)” chỉ tính khi thực tế phát sinh.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>- Các khoản ghi “Ước tính” chưa phải chi phí chắc chắn, sẽ xác nhận lại trước khi thực hiện.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Rất mong được hợp tác cùng Quý khách.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="F56" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Báo giá là dự toán, chưa phải hóa đơn hoặc nghĩa vụ thanh toán. Thuế dự kiến không thay thế kết luận pháp lý / hải quan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>CÔNG TY TNHH GIAO NHẬN QUỐC TẾ TRƯỜNG THÀNH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A18:I18"/>
+  <mergeCells count="3">
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A19:I19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
